--- a/data/trans_dic/P33B_R1-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P33B_R1-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,37; 13,54</t>
+          <t>6,11; 12,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,69; 17,35</t>
+          <t>11,77; 17,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,66; 14,38</t>
+          <t>9,71; 13,99</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,47; 11,66</t>
+          <t>5,12; 10,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,08; 13,53</t>
+          <t>8,47; 12,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,88; 11,77</t>
+          <t>7,57; 11,41</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,22; 17,34</t>
+          <t>10,48; 17,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,13; 25,29</t>
+          <t>18,17; 25,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,43; 20,4</t>
+          <t>15,56; 20,75</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>18,2%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,3; 19,51</t>
+          <t>9,51; 17,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,38; 23,52</t>
+          <t>19,22; 26,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,92; 19,81</t>
+          <t>15,43; 21,01</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,01; 11,19</t>
+          <t>4,63; 10,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,5; 13,86</t>
+          <t>8,59; 13,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,64; 11,75</t>
+          <t>7,42; 11,16</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,31; 15,0</t>
+          <t>8,05; 14,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19,93; 27,78</t>
+          <t>20,1; 28,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,7; 19,73</t>
+          <t>14,95; 19,82</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,55; 15,91</t>
+          <t>9,8; 15,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,66; 22,5</t>
+          <t>19,6; 25,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,61; 17,76</t>
+          <t>15,62; 19,77</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>25,21%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,04; 21,29</t>
+          <t>16,89; 22,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>28,37; 34,01</t>
+          <t>27,85; 33,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,69; 26,43</t>
+          <t>23,27; 27,25</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9,57; 13,55</t>
+          <t>11,63; 13,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15,35; 21,09</t>
+          <t>20,16; 22,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13,7; 17,06</t>
+          <t>16,29; 18,02</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29058</t>
+          <t>28422</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41650</t>
+          <t>45232</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70708</t>
+          <t>73654</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19853; 42182</t>
+          <t>19481; 38479</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33862; 50253</t>
+          <t>37201; 54608</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>58042; 86408</t>
+          <t>61668; 88855</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>40754</t>
+          <t>40442</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>57573</t>
+          <t>58834</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>98327</t>
+          <t>99276</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28374; 60423</t>
+          <t>27154; 57795</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46749; 69694</t>
+          <t>46293; 70866</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>81459; 121647</t>
+          <t>81579; 122881</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>43203</t>
+          <t>43915</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76051</t>
+          <t>77381</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>119254</t>
+          <t>121296</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>32310; 54793</t>
+          <t>33117; 56147</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>63116; 88025</t>
+          <t>64561; 90522</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>102497; 135485</t>
+          <t>104423; 139254</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>44821</t>
+          <t>49646</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>85768</t>
+          <t>95081</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>130589</t>
+          <t>144727</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32182; 60994</t>
+          <t>35481; 66913</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>54137; 111873</t>
+          <t>81081; 113321</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>93989; 156168</t>
+          <t>122710; 167055</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13665</t>
+          <t>14545</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22868</t>
+          <t>25031</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36532</t>
+          <t>39576</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8962; 19994</t>
+          <t>9531; 21903</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17701; 28873</t>
+          <t>19493; 31223</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>29572; 45460</t>
+          <t>32098; 48282</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>30093</t>
+          <t>30084</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>60352</t>
+          <t>62891</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>90445</t>
+          <t>92975</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>22410; 40434</t>
+          <t>21791; 40320</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>51225; 71411</t>
+          <t>53024; 74242</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>77448; 103940</t>
+          <t>79901; 105924</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>76439</t>
+          <t>87726</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>139097</t>
+          <t>173594</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>215537</t>
+          <t>261320</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>59522; 99172</t>
+          <t>70445; 110589</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>65066; 191055</t>
+          <t>151330; 195279</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>141497; 261449</t>
+          <t>232826; 294654</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>138211</t>
+          <t>154567</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>222701</t>
+          <t>255948</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>360912</t>
+          <t>410515</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>65374; 197729</t>
+          <t>134810; 176044</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>202936; 243335</t>
+          <t>231288; 277861</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>225109; 434513</t>
+          <t>378957; 443796</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>416243</t>
+          <t>449347</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>706060</t>
+          <t>793993</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1122303</t>
+          <t>1243340</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>331078; 468750</t>
+          <t>410856; 488805</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>561591; 771546</t>
+          <t>752721; 835932</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>975390; 1214311</t>
+          <t>1183311; 1308982</t>
         </is>
       </c>
     </row>
